--- a/Money supply.xlsx
+++ b/Money supply.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1.3" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="1.3" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <externalReferences>
-    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+    <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames>
     <definedName name="_AMO_XmlVersion" hidden="1">"'1'"</definedName>
@@ -766,8 +766,8 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+<externalLink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook r:id="rId1">
     <sheetNames>
       <sheetName val="Sheet1"/>
       <sheetName val="Input"/>
@@ -1127,7 +1127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P169"/>
+  <dimension ref="A1:P170"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.90625" defaultRowHeight="13"/>
   <cols>
     <col width="5.6328125" customWidth="1" style="10" min="1" max="1"/>
@@ -9040,7 +9040,50 @@
         <v>6598.71242499957</v>
       </c>
     </row>
-    <row r="170" ht="10.5" customFormat="1" customHeight="1" s="6"/>
+    <row r="170" ht="10.5" customFormat="1" customHeight="1" s="6">
+      <c r="B170" t="n">
+        <v>4</v>
+      </c>
+      <c r="D170" t="n">
+        <v>2627554.53339764</v>
+      </c>
+      <c r="E170" t="n">
+        <v>2621759.49293864</v>
+      </c>
+      <c r="F170" t="n">
+        <v>727608.76059864</v>
+      </c>
+      <c r="G170" t="n">
+        <v>170522.55428964</v>
+      </c>
+      <c r="H170" t="n">
+        <v>557086.206309</v>
+      </c>
+      <c r="I170" t="n">
+        <v>1894150.73234</v>
+      </c>
+      <c r="J170" t="n">
+        <v>250273.367201</v>
+      </c>
+      <c r="K170" t="n">
+        <v>1076117.9049</v>
+      </c>
+      <c r="L170" t="n">
+        <v>1392.46449</v>
+      </c>
+      <c r="M170" t="n">
+        <v>791.44594</v>
+      </c>
+      <c r="N170" t="n">
+        <v>323671.425759</v>
+      </c>
+      <c r="O170" t="n">
+        <v>241904.12405</v>
+      </c>
+      <c r="P170" t="n">
+        <v>5795.04045900051</v>
+      </c>
+    </row>
     <row r="171" ht="14.5" customFormat="1" customHeight="1" s="6"/>
     <row r="172" ht="14.5" customHeight="1"/>
     <row r="173" ht="14.5" customHeight="1"/>

--- a/Money supply.xlsx
+++ b/Money supply.xlsx
@@ -1127,7 +1127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P170"/>
+  <dimension ref="A1:P171"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.90625" defaultRowHeight="13"/>
   <cols>
     <col width="5.6328125" customWidth="1" style="10" min="1" max="1"/>
@@ -9084,7 +9084,50 @@
         <v>5795.04045900051</v>
       </c>
     </row>
-    <row r="171" ht="14.5" customFormat="1" customHeight="1" s="6"/>
+    <row r="171" ht="14.5" customFormat="1" customHeight="1" s="6">
+      <c r="B171" t="n">
+        <v>5</v>
+      </c>
+      <c r="D171" t="n">
+        <v>2639803.45804345</v>
+      </c>
+      <c r="E171" t="n">
+        <v>2634863.11806945</v>
+      </c>
+      <c r="F171" t="n">
+        <v>738502.32454245</v>
+      </c>
+      <c r="G171" t="n">
+        <v>171101.09330645</v>
+      </c>
+      <c r="H171" t="n">
+        <v>567401.231236</v>
+      </c>
+      <c r="I171" t="n">
+        <v>1896360.793527</v>
+      </c>
+      <c r="J171" t="n">
+        <v>246965.067818</v>
+      </c>
+      <c r="K171" t="n">
+        <v>1078033.348421</v>
+      </c>
+      <c r="L171" t="n">
+        <v>1841.226262</v>
+      </c>
+      <c r="M171" t="n">
+        <v>791.400162</v>
+      </c>
+      <c r="N171" t="n">
+        <v>334824.618088</v>
+      </c>
+      <c r="O171" t="n">
+        <v>233905.132776</v>
+      </c>
+      <c r="P171" t="n">
+        <v>4940.33997399965</v>
+      </c>
+    </row>
     <row r="172" ht="14.5" customHeight="1"/>
     <row r="173" ht="14.5" customHeight="1"/>
     <row r="174" ht="14.5" customHeight="1"/>
